--- a/artfynd/A 26178-2025 artfynd.xlsx
+++ b/artfynd/A 26178-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125707751</v>
+        <v>125707758</v>
       </c>
       <c r="B4" t="n">
-        <v>101410</v>
+        <v>100506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519744</v>
+        <v>519748</v>
       </c>
       <c r="R4" t="n">
-        <v>6967751</v>
+        <v>6967726</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125707758</v>
+        <v>125707751</v>
       </c>
       <c r="B5" t="n">
-        <v>100506</v>
+        <v>101410</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519748</v>
+        <v>519744</v>
       </c>
       <c r="R5" t="n">
-        <v>6967726</v>
+        <v>6967751</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 26178-2025 artfynd.xlsx
+++ b/artfynd/A 26178-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125707830</v>
       </c>
       <c r="B2" t="n">
-        <v>101410</v>
+        <v>101417</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125707889</v>
       </c>
       <c r="B3" t="n">
-        <v>101410</v>
+        <v>101417</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125707758</v>
+        <v>125707751</v>
       </c>
       <c r="B4" t="n">
-        <v>100506</v>
+        <v>101417</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519748</v>
+        <v>519744</v>
       </c>
       <c r="R4" t="n">
-        <v>6967726</v>
+        <v>6967751</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125707751</v>
+        <v>125707758</v>
       </c>
       <c r="B5" t="n">
-        <v>101410</v>
+        <v>100513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519744</v>
+        <v>519748</v>
       </c>
       <c r="R5" t="n">
-        <v>6967751</v>
+        <v>6967726</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125708601</v>
       </c>
       <c r="B6" t="n">
-        <v>101410</v>
+        <v>101417</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26178-2025 artfynd.xlsx
+++ b/artfynd/A 26178-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125707830</v>
       </c>
       <c r="B2" t="n">
-        <v>101417</v>
+        <v>101420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125707889</v>
       </c>
       <c r="B3" t="n">
-        <v>101417</v>
+        <v>101420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125707751</v>
       </c>
       <c r="B4" t="n">
-        <v>101417</v>
+        <v>101420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125707758</v>
       </c>
       <c r="B5" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125708601</v>
       </c>
       <c r="B6" t="n">
-        <v>101417</v>
+        <v>101420</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26178-2025 artfynd.xlsx
+++ b/artfynd/A 26178-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125707830</v>
       </c>
       <c r="B2" t="n">
-        <v>101420</v>
+        <v>101424</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125707889</v>
       </c>
       <c r="B3" t="n">
-        <v>101420</v>
+        <v>101424</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125707751</v>
+        <v>125707758</v>
       </c>
       <c r="B4" t="n">
-        <v>101420</v>
+        <v>100520</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519744</v>
+        <v>519748</v>
       </c>
       <c r="R4" t="n">
-        <v>6967751</v>
+        <v>6967726</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125707758</v>
+        <v>125707751</v>
       </c>
       <c r="B5" t="n">
-        <v>100516</v>
+        <v>101424</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519748</v>
+        <v>519744</v>
       </c>
       <c r="R5" t="n">
-        <v>6967726</v>
+        <v>6967751</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125708601</v>
       </c>
       <c r="B6" t="n">
-        <v>101420</v>
+        <v>101424</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26178-2025 artfynd.xlsx
+++ b/artfynd/A 26178-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125707830</v>
       </c>
       <c r="B2" t="n">
-        <v>101424</v>
+        <v>101425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125707889</v>
       </c>
       <c r="B3" t="n">
-        <v>101424</v>
+        <v>101425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125707758</v>
+        <v>125707751</v>
       </c>
       <c r="B4" t="n">
-        <v>100520</v>
+        <v>101425</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519748</v>
+        <v>519744</v>
       </c>
       <c r="R4" t="n">
-        <v>6967726</v>
+        <v>6967751</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125707751</v>
+        <v>125707758</v>
       </c>
       <c r="B5" t="n">
-        <v>101424</v>
+        <v>100521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519744</v>
+        <v>519748</v>
       </c>
       <c r="R5" t="n">
-        <v>6967751</v>
+        <v>6967726</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125708601</v>
       </c>
       <c r="B6" t="n">
-        <v>101424</v>
+        <v>101425</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26178-2025 artfynd.xlsx
+++ b/artfynd/A 26178-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125707830</v>
       </c>
       <c r="B2" t="n">
-        <v>101425</v>
+        <v>101427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125707889</v>
       </c>
       <c r="B3" t="n">
-        <v>101425</v>
+        <v>101427</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125707751</v>
       </c>
       <c r="B4" t="n">
-        <v>101425</v>
+        <v>101427</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125707758</v>
       </c>
       <c r="B5" t="n">
-        <v>100521</v>
+        <v>100523</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125708601</v>
       </c>
       <c r="B6" t="n">
-        <v>101425</v>
+        <v>101427</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26178-2025 artfynd.xlsx
+++ b/artfynd/A 26178-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125707830</v>
       </c>
       <c r="B2" t="n">
-        <v>101427</v>
+        <v>101429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125707889</v>
       </c>
       <c r="B3" t="n">
-        <v>101427</v>
+        <v>101429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125707751</v>
       </c>
       <c r="B4" t="n">
-        <v>101427</v>
+        <v>101429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125707758</v>
       </c>
       <c r="B5" t="n">
-        <v>100523</v>
+        <v>100525</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125708601</v>
       </c>
       <c r="B6" t="n">
-        <v>101427</v>
+        <v>101429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26178-2025 artfynd.xlsx
+++ b/artfynd/A 26178-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125707830</v>
       </c>
       <c r="B2" t="n">
-        <v>101429</v>
+        <v>101431</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125707889</v>
       </c>
       <c r="B3" t="n">
-        <v>101429</v>
+        <v>101431</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125707751</v>
+        <v>125707758</v>
       </c>
       <c r="B4" t="n">
-        <v>101429</v>
+        <v>100527</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519744</v>
+        <v>519748</v>
       </c>
       <c r="R4" t="n">
-        <v>6967751</v>
+        <v>6967726</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125707758</v>
+        <v>125707751</v>
       </c>
       <c r="B5" t="n">
-        <v>100525</v>
+        <v>101431</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519748</v>
+        <v>519744</v>
       </c>
       <c r="R5" t="n">
-        <v>6967726</v>
+        <v>6967751</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125708601</v>
       </c>
       <c r="B6" t="n">
-        <v>101429</v>
+        <v>101431</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26178-2025 artfynd.xlsx
+++ b/artfynd/A 26178-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125707830</v>
       </c>
       <c r="B2" t="n">
-        <v>101431</v>
+        <v>101435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125707889</v>
       </c>
       <c r="B3" t="n">
-        <v>101431</v>
+        <v>101435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125707758</v>
+        <v>125707751</v>
       </c>
       <c r="B4" t="n">
-        <v>100527</v>
+        <v>101435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519748</v>
+        <v>519744</v>
       </c>
       <c r="R4" t="n">
-        <v>6967726</v>
+        <v>6967751</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125707751</v>
+        <v>125707758</v>
       </c>
       <c r="B5" t="n">
-        <v>101431</v>
+        <v>100531</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519744</v>
+        <v>519748</v>
       </c>
       <c r="R5" t="n">
-        <v>6967751</v>
+        <v>6967726</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125708601</v>
       </c>
       <c r="B6" t="n">
-        <v>101431</v>
+        <v>101435</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26178-2025 artfynd.xlsx
+++ b/artfynd/A 26178-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125707830</v>
       </c>
       <c r="B2" t="n">
-        <v>101435</v>
+        <v>101438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125707889</v>
       </c>
       <c r="B3" t="n">
-        <v>101435</v>
+        <v>101438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125707751</v>
       </c>
       <c r="B4" t="n">
-        <v>101435</v>
+        <v>101438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125707758</v>
       </c>
       <c r="B5" t="n">
-        <v>100531</v>
+        <v>100534</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125708601</v>
       </c>
       <c r="B6" t="n">
-        <v>101435</v>
+        <v>101438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
